--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Rb6fdb106171c4dad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R07c07203aa794a72"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -310,7 +310,7 @@
         <x:v>攻击间隔最低倍率</x:v>
       </x:c>
       <x:c r="H1" s="5" t="str">
-        <x:v>单局免费换卡次数</x:v>
+        <x:v>每次三选一广告刷新次数</x:v>
       </x:c>
       <x:c r="I1" s="5" t="str">
         <x:v>试玩全部店员</x:v>
@@ -424,7 +424,7 @@
         <x:v>攻击间隔最低倍率</x:v>
       </x:c>
       <x:c r="H4" s="5" t="str">
-        <x:v>单局免费换卡次数</x:v>
+        <x:v>每次广告刷新次数</x:v>
       </x:c>
       <x:c r="I4" s="5" t="str">
         <x:v>试玩全部店员</x:v>
@@ -462,7 +462,7 @@
         <x:v>minIntervalRatio</x:v>
       </x:c>
       <x:c r="H5" s="5" t="str">
-        <x:v>freeRefresh</x:v>
+        <x:v>adRefreshPerChoice</x:v>
       </x:c>
       <x:c r="I5" s="5" t="str">
         <x:v>allowAllStaff</x:v>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R07c07203aa794a72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R8826e3d2b4f94236"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -515,6 +515,196 @@
         <x:v>0.3</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G7" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L7" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="H8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L8" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="H9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L9" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G10" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="H10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L10" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="H11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L11" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R8826e3d2b4f94236"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Rd4df5817825a4536"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -285,6 +285,8 @@
     <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="23.75" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="23.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
@@ -324,6 +326,12 @@
       <x:c r="L1" s="6" t="str">
         <x:v>复活后敌人最远路线比例</x:v>
       </x:c>
+      <x:c r="M1" s="6" t="str">
+        <x:v>怪群击败收益折算</x:v>
+      </x:c>
+      <x:c r="N1" s="6" t="str">
+        <x:v>挑战首领移速比例</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="40" customHeight="1">
       <x:c r="A2" s="5" t="str">
@@ -360,6 +368,12 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="L2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="M2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="N2" s="6" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -400,6 +414,12 @@
       <x:c r="L3" s="6" t="str">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="M3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="N3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="5" t="str">
@@ -438,6 +458,12 @@
       <x:c r="L4" s="6" t="str">
         <x:v>复活后敌人最远路线比例</x:v>
       </x:c>
+      <x:c r="M4" s="6" t="str">
+        <x:v>killRewardRatio</x:v>
+      </x:c>
+      <x:c r="N4" s="6" t="str">
+        <x:v>bossSpeedRatio</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="40" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -476,6 +502,12 @@
       <x:c r="L5" s="6" t="str">
         <x:v>reviveProgress</x:v>
       </x:c>
+      <x:c r="M5" s="6" t="str">
+        <x:v>killRewardRatio</x:v>
+      </x:c>
+      <x:c r="N5" s="6" t="str">
+        <x:v>bossSpeedRatio</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="40" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -494,10 +526,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="7" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="7" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="H6" s="7" t="n">
         <x:v>1</x:v>
@@ -513,6 +545,12 @@
       </x:c>
       <x:c r="L6" s="8" t="n">
         <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M6" s="8" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="N6" s="8" t="n">
+        <x:v>0.65</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -532,10 +570,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G7" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="H7" t="n">
         <x:v>1</x:v>
@@ -551,6 +589,12 @@
       </x:c>
       <x:c r="L7" t="n">
         <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="N7" t="n">
+        <x:v>0.65</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -570,10 +614,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G8" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="H8" t="n">
         <x:v>1</x:v>
@@ -589,6 +633,12 @@
       </x:c>
       <x:c r="L8" t="n">
         <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="N8" t="n">
+        <x:v>0.65</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -608,10 +658,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G9" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="H9" t="n">
         <x:v>1</x:v>
@@ -627,6 +677,12 @@
       </x:c>
       <x:c r="L9" t="n">
         <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="N9" t="n">
+        <x:v>0.65</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -646,10 +702,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G10" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="H10" t="n">
         <x:v>1</x:v>
@@ -665,6 +721,12 @@
       </x:c>
       <x:c r="L10" t="n">
         <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M10" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="N10" t="n">
+        <x:v>0.65</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -684,10 +746,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="H11" t="n">
         <x:v>1</x:v>
@@ -703,6 +765,12 @@
       </x:c>
       <x:c r="L11" t="n">
         <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="N11" t="n">
+        <x:v>0.55</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Rd4df5817825a4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R9c51a4a815994a0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -287,6 +287,21 @@
     <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="23.75" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="23.75" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="20" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="20" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="20" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="20" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="20" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="20" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="20" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="20" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="20" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
@@ -332,6 +347,51 @@
       <x:c r="N1" s="6" t="str">
         <x:v>挑战首领移速比例</x:v>
       </x:c>
+      <x:c r="O1" s="6" t="str">
+        <x:v>道路两列偏移</x:v>
+      </x:c>
+      <x:c r="P1" s="6" t="str">
+        <x:v>身体安全间距</x:v>
+      </x:c>
+      <x:c r="Q1" s="6" t="str">
+        <x:v>怪潮阶段游戏秒</x:v>
+      </x:c>
+      <x:c r="R1" s="6" t="str">
+        <x:v>每几名出现精英</x:v>
+      </x:c>
+      <x:c r="S1" s="6" t="str">
+        <x:v>精英出现阶段</x:v>
+      </x:c>
+      <x:c r="T1" s="6" t="str">
+        <x:v>精英耐久倍率</x:v>
+      </x:c>
+      <x:c r="U1" s="6" t="str">
+        <x:v>精英每阶段成长</x:v>
+      </x:c>
+      <x:c r="V1" s="6" t="str">
+        <x:v>精英身体倍率</x:v>
+      </x:c>
+      <x:c r="W1" s="6" t="str">
+        <x:v>精英速度倍率</x:v>
+      </x:c>
+      <x:c r="X1" s="6" t="str">
+        <x:v>精英收益倍率</x:v>
+      </x:c>
+      <x:c r="Y1" s="6" t="str">
+        <x:v>专属成长阶段数</x:v>
+      </x:c>
+      <x:c r="Z1" s="6" t="str">
+        <x:v>专属每阶伤害</x:v>
+      </x:c>
+      <x:c r="AA1" s="6" t="str">
+        <x:v>专属每阶范围</x:v>
+      </x:c>
+      <x:c r="AB1" s="6" t="str">
+        <x:v>普通怪每阶段提速</x:v>
+      </x:c>
+      <x:c r="AC1" s="6" t="str">
+        <x:v>挑战首领入店伤害</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="40" customHeight="1">
       <x:c r="A2" s="5" t="str">
@@ -374,6 +434,51 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="N2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="O2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="P2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="Q2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="R2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="S2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="T2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="U2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="V2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="W2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="X2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="Y2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="Z2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AA2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AB2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AC2" s="6" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -420,6 +525,51 @@
       <x:c r="N3" s="6" t="str">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="O3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="P3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Q3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="R3" s="6" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="S3" s="6" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="T3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="U3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="V3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="W3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="X3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Y3" s="6" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="Z3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AA3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AB3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AC3" s="6" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="5" t="str">
@@ -464,6 +614,51 @@
       <x:c r="N4" s="6" t="str">
         <x:v>bossSpeedRatio</x:v>
       </x:c>
+      <x:c r="O4" s="6" t="str">
+        <x:v>laneOffset</x:v>
+      </x:c>
+      <x:c r="P4" s="6" t="str">
+        <x:v>crowdGap</x:v>
+      </x:c>
+      <x:c r="Q4" s="6" t="str">
+        <x:v>waveDuration</x:v>
+      </x:c>
+      <x:c r="R4" s="6" t="str">
+        <x:v>eliteEvery</x:v>
+      </x:c>
+      <x:c r="S4" s="6" t="str">
+        <x:v>eliteStartWave</x:v>
+      </x:c>
+      <x:c r="T4" s="6" t="str">
+        <x:v>eliteHealthScale</x:v>
+      </x:c>
+      <x:c r="U4" s="6" t="str">
+        <x:v>eliteHealthGrowth</x:v>
+      </x:c>
+      <x:c r="V4" s="6" t="str">
+        <x:v>eliteScale</x:v>
+      </x:c>
+      <x:c r="W4" s="6" t="str">
+        <x:v>eliteSpeedRatio</x:v>
+      </x:c>
+      <x:c r="X4" s="6" t="str">
+        <x:v>eliteRewardRatio</x:v>
+      </x:c>
+      <x:c r="Y4" s="6" t="str">
+        <x:v>growthEvery</x:v>
+      </x:c>
+      <x:c r="Z4" s="6" t="str">
+        <x:v>growthDamage</x:v>
+      </x:c>
+      <x:c r="AA4" s="6" t="str">
+        <x:v>growthRange</x:v>
+      </x:c>
+      <x:c r="AB4" s="6" t="str">
+        <x:v>crowdSpeedGrowth</x:v>
+      </x:c>
+      <x:c r="AC4" s="6" t="str">
+        <x:v>bossLeakDamage</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="40" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -508,6 +703,51 @@
       <x:c r="N5" s="6" t="str">
         <x:v>bossSpeedRatio</x:v>
       </x:c>
+      <x:c r="O5" s="6" t="str">
+        <x:v>laneOffset</x:v>
+      </x:c>
+      <x:c r="P5" s="6" t="str">
+        <x:v>crowdGap</x:v>
+      </x:c>
+      <x:c r="Q5" s="6" t="str">
+        <x:v>waveDuration</x:v>
+      </x:c>
+      <x:c r="R5" s="6" t="str">
+        <x:v>eliteEvery</x:v>
+      </x:c>
+      <x:c r="S5" s="6" t="str">
+        <x:v>eliteStartWave</x:v>
+      </x:c>
+      <x:c r="T5" s="6" t="str">
+        <x:v>eliteHealthScale</x:v>
+      </x:c>
+      <x:c r="U5" s="6" t="str">
+        <x:v>eliteHealthGrowth</x:v>
+      </x:c>
+      <x:c r="V5" s="6" t="str">
+        <x:v>eliteScale</x:v>
+      </x:c>
+      <x:c r="W5" s="6" t="str">
+        <x:v>eliteSpeedRatio</x:v>
+      </x:c>
+      <x:c r="X5" s="6" t="str">
+        <x:v>eliteRewardRatio</x:v>
+      </x:c>
+      <x:c r="Y5" s="6" t="str">
+        <x:v>growthEvery</x:v>
+      </x:c>
+      <x:c r="Z5" s="6" t="str">
+        <x:v>growthDamage</x:v>
+      </x:c>
+      <x:c r="AA5" s="6" t="str">
+        <x:v>growthRange</x:v>
+      </x:c>
+      <x:c r="AB5" s="6" t="str">
+        <x:v>crowdSpeedGrowth</x:v>
+      </x:c>
+      <x:c r="AC5" s="6" t="str">
+        <x:v>bossLeakDamage</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="40" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -526,7 +766,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G6" s="7" t="n">
         <x:v>0.6</x:v>
@@ -547,10 +787,55 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M6" s="8" t="n">
-        <x:v>0.055</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="N6" s="8" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O6" s="8" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P6" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q6" s="8" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="R6" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S6" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T6" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U6" s="8" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="V6" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W6" s="8" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X6" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y6" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Z6" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA6" s="8" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB6" s="8" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="AC6" s="8" t="n">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -570,7 +855,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G7" t="n">
         <x:v>0.6</x:v>
@@ -591,10 +876,55 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M7" t="n">
-        <x:v>0.055</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="N7" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O7" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q7" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="R7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U7" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="V7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W7" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Z7" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA7" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB7" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="AC7" t="n">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -614,7 +944,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G8" t="n">
         <x:v>0.6</x:v>
@@ -635,10 +965,55 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M8" t="n">
-        <x:v>0.055</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="N8" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O8" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q8" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="R8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U8" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="V8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W8" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Z8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA8" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB8" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="AC8" t="n">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -658,7 +1033,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G9" t="n">
         <x:v>0.6</x:v>
@@ -679,10 +1054,55 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M9" t="n">
-        <x:v>0.055</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="N9" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O9" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="R9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U9" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="V9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W9" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Z9" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA9" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB9" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="AC9" t="n">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -702,7 +1122,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G10" t="n">
         <x:v>0.6</x:v>
@@ -723,10 +1143,55 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M10" t="n">
-        <x:v>0.055</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="N10" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O10" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q10" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="R10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U10" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="V10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W10" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Z10" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA10" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB10" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="AC10" t="n">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -746,7 +1211,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F11" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G11" t="n">
         <x:v>0.6</x:v>
@@ -767,10 +1232,55 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M11" t="n">
-        <x:v>0.055</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="N11" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O11" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q11" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="R11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U11" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="V11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W11" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Z11" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA11" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB11" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="AC11" t="n">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R9c51a4a815994a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Rdf83df5702ad4cd5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -808,10 +808,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T6" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="U6" s="8" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="V6" s="8" t="n">
         <x:v>1</x:v>
@@ -897,10 +897,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T7" t="n">
-        <x:v>4</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="U7" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="V7" t="n">
         <x:v>1</x:v>
@@ -986,10 +986,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T8" t="n">
-        <x:v>4</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="U8" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="V8" t="n">
         <x:v>1</x:v>
@@ -1075,10 +1075,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T9" t="n">
-        <x:v>4</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="U9" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="V9" t="n">
         <x:v>1</x:v>
@@ -1164,10 +1164,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T10" t="n">
-        <x:v>4</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="U10" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="V10" t="n">
         <x:v>1</x:v>
@@ -1253,10 +1253,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T11" t="n">
-        <x:v>4</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="U11" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="V11" t="n">
         <x:v>1</x:v>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Rdf83df5702ad4cd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R2ca9605d9e9740ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -302,6 +302,8 @@
     <x:col min="27" max="27" width="20" hidden="0" customWidth="1"/>
     <x:col min="28" max="28" width="20" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="20" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="22.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
@@ -392,6 +394,12 @@
       <x:c r="AC1" s="6" t="str">
         <x:v>挑战首领入店伤害</x:v>
       </x:c>
+      <x:c r="AD1" s="6" t="str">
+        <x:v>波内末段新生血量增幅</x:v>
+      </x:c>
+      <x:c r="AE1" s="6" t="str">
+        <x:v>波内血量成长曲线指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="40" customHeight="1">
       <x:c r="A2" s="5" t="str">
@@ -479,6 +487,12 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="AC2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AD2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AE2" s="6" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -570,6 +584,12 @@
       <x:c r="AC3" s="6" t="str">
         <x:v>int</x:v>
       </x:c>
+      <x:c r="AD3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AE3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="5" t="str">
@@ -659,6 +679,12 @@
       <x:c r="AC4" s="6" t="str">
         <x:v>bossLeakDamage</x:v>
       </x:c>
+      <x:c r="AD4" s="6" t="str">
+        <x:v>phaseHealthGrowth</x:v>
+      </x:c>
+      <x:c r="AE4" s="6" t="str">
+        <x:v>phaseGrowthPower</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="40" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -748,6 +774,12 @@
       <x:c r="AC5" s="6" t="str">
         <x:v>bossLeakDamage</x:v>
       </x:c>
+      <x:c r="AD5" s="6" t="str">
+        <x:v>phaseHealthGrowth</x:v>
+      </x:c>
+      <x:c r="AE5" s="6" t="str">
+        <x:v>phaseGrowthPower</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="40" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -836,6 +868,12 @@
       </x:c>
       <x:c r="AC6" s="8" t="n">
         <x:v>20</x:v>
+      </x:c>
+      <x:c r="AD6" s="8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="AE6" s="8" t="n">
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -926,6 +964,12 @@
       <x:c r="AC7" t="n">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="AD7" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="AE7" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="n">
@@ -1015,6 +1059,12 @@
       <x:c r="AC8" t="n">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="AD8" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="AE8" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="n">
@@ -1104,6 +1154,12 @@
       <x:c r="AC9" t="n">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="AD9" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="AE9" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="n">
@@ -1193,6 +1249,12 @@
       <x:c r="AC10" t="n">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="AD10" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="AE10" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="n">
@@ -1281,6 +1343,12 @@
       </x:c>
       <x:c r="AC11" t="n">
         <x:v>20</x:v>
+      </x:c>
+      <x:c r="AD11" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="AE11" t="n">
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R2ca9605d9e9740ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R9159e5149b284f3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -304,6 +304,9 @@
     <x:col min="29" max="29" width="20" hidden="0" customWidth="1"/>
     <x:col min="30" max="30" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="31" max="31" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="21.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="21.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="21.8799991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
@@ -400,6 +403,15 @@
       <x:c r="AE1" s="6" t="str">
         <x:v>波内血量成长曲线指数</x:v>
       </x:c>
+      <x:c r="AF1" s="6" t="str">
+        <x:v>波末收尾真实秒数</x:v>
+      </x:c>
+      <x:c r="AG1" s="6" t="str">
+        <x:v>补给淡入真实秒数</x:v>
+      </x:c>
+      <x:c r="AH1" s="6" t="str">
+        <x:v>波末衔接下一波基础血量</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="40" customHeight="1">
       <x:c r="A2" s="5" t="str">
@@ -493,6 +505,15 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="AE2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AF2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AG2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AH2" s="6" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -590,6 +611,15 @@
       <x:c r="AE3" s="6" t="str">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="AF3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AG3" s="6" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AH3" s="6" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="5" t="str">
@@ -685,6 +715,15 @@
       <x:c r="AE4" s="6" t="str">
         <x:v>phaseGrowthPower</x:v>
       </x:c>
+      <x:c r="AF4" s="6" t="str">
+        <x:v>supplyDelay</x:v>
+      </x:c>
+      <x:c r="AG4" s="6" t="str">
+        <x:v>supplyFadeDuration</x:v>
+      </x:c>
+      <x:c r="AH4" s="6" t="str">
+        <x:v>phaseFollowNextWave</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="40" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -780,6 +819,15 @@
       <x:c r="AE5" s="6" t="str">
         <x:v>phaseGrowthPower</x:v>
       </x:c>
+      <x:c r="AF5" s="6" t="str">
+        <x:v>supplyDelay</x:v>
+      </x:c>
+      <x:c r="AG5" s="6" t="str">
+        <x:v>supplyFadeDuration</x:v>
+      </x:c>
+      <x:c r="AH5" s="6" t="str">
+        <x:v>phaseFollowNextWave</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="40" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -792,13 +840,13 @@
         <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
       </x:c>
       <x:c r="D6" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="G6" s="7" t="n">
         <x:v>0.6</x:v>
@@ -870,10 +918,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD6" s="8" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="AE6" s="8" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF6" s="8" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG6" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH6" s="8" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -887,13 +944,13 @@
         <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="G7" t="n">
         <x:v>0.6</x:v>
@@ -965,10 +1022,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD7" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="AE7" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF7" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG7" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH7" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -982,13 +1048,13 @@
         <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
       </x:c>
       <x:c r="D8" t="n">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E8" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="G8" t="n">
         <x:v>0.6</x:v>
@@ -1060,10 +1126,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD8" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="AE8" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF8" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH8" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1077,13 +1152,13 @@
         <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
       </x:c>
       <x:c r="D9" t="n">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E9" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="G9" t="n">
         <x:v>0.6</x:v>
@@ -1155,10 +1230,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD9" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="AE9" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF9" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG9" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH9" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1172,13 +1256,13 @@
         <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
       </x:c>
       <x:c r="D10" t="n">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E10" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="G10" t="n">
         <x:v>0.6</x:v>
@@ -1250,10 +1334,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD10" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="AE10" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF10" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG10" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH10" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1267,13 +1360,13 @@
         <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
       </x:c>
       <x:c r="D11" t="n">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F11" t="n">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="G11" t="n">
         <x:v>0.6</x:v>
@@ -1345,10 +1438,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD11" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="AE11" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF11" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG11" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH11" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R9159e5149b284f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Ra394f54386cd4331"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -837,10 +837,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
       </x:c>
       <x:c r="D6" s="7" t="n">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
         <x:v>10</x:v>
@@ -867,7 +867,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M6" s="8" t="n">
-        <x:v>0.085</x:v>
+        <x:v>0.053125</x:v>
       </x:c>
       <x:c r="N6" s="8" t="n">
         <x:v>0.9</x:v>
@@ -879,19 +879,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q6" s="8" t="n">
-        <x:v>175</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="R6" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S6" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T6" s="8" t="n">
         <x:v>4.5</x:v>
       </x:c>
       <x:c r="U6" s="8" t="n">
-        <x:v>0.14</x:v>
+        <x:v>0.0672</x:v>
       </x:c>
       <x:c r="V6" s="8" t="n">
         <x:v>1</x:v>
@@ -903,7 +903,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Y6" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="Z6" s="8" t="n">
         <x:v>0.25</x:v>
@@ -912,7 +912,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="AB6" s="8" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.01207</x:v>
       </x:c>
       <x:c r="AC6" s="8" t="n">
         <x:v>20</x:v>
@@ -941,10 +941,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E7" t="n">
         <x:v>10</x:v>
@@ -971,7 +971,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M7" t="n">
-        <x:v>0.085</x:v>
+        <x:v>0.053125</x:v>
       </x:c>
       <x:c r="N7" t="n">
         <x:v>0.9</x:v>
@@ -983,19 +983,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q7" t="n">
-        <x:v>175</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="R7" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T7" t="n">
         <x:v>4.5</x:v>
       </x:c>
       <x:c r="U7" t="n">
-        <x:v>0.14</x:v>
+        <x:v>0.0672</x:v>
       </x:c>
       <x:c r="V7" t="n">
         <x:v>1</x:v>
@@ -1007,7 +1007,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Y7" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="Z7" t="n">
         <x:v>0.25</x:v>
@@ -1016,7 +1016,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="AB7" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.01207</x:v>
       </x:c>
       <x:c r="AC7" t="n">
         <x:v>20</x:v>
@@ -1045,10 +1045,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
       </x:c>
       <x:c r="D8" t="n">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E8" t="n">
         <x:v>10</x:v>
@@ -1075,7 +1075,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M8" t="n">
-        <x:v>0.085</x:v>
+        <x:v>0.053125</x:v>
       </x:c>
       <x:c r="N8" t="n">
         <x:v>0.9</x:v>
@@ -1087,19 +1087,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q8" t="n">
-        <x:v>175</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="R8" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T8" t="n">
         <x:v>4.5</x:v>
       </x:c>
       <x:c r="U8" t="n">
-        <x:v>0.14</x:v>
+        <x:v>0.0672</x:v>
       </x:c>
       <x:c r="V8" t="n">
         <x:v>1</x:v>
@@ -1111,7 +1111,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Y8" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="Z8" t="n">
         <x:v>0.25</x:v>
@@ -1120,7 +1120,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="AB8" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.01207</x:v>
       </x:c>
       <x:c r="AC8" t="n">
         <x:v>20</x:v>
@@ -1149,10 +1149,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
       </x:c>
       <x:c r="D9" t="n">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E9" t="n">
         <x:v>10</x:v>
@@ -1179,7 +1179,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M9" t="n">
-        <x:v>0.085</x:v>
+        <x:v>0.053125</x:v>
       </x:c>
       <x:c r="N9" t="n">
         <x:v>0.9</x:v>
@@ -1191,19 +1191,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q9" t="n">
-        <x:v>175</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="R9" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S9" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T9" t="n">
         <x:v>4.5</x:v>
       </x:c>
       <x:c r="U9" t="n">
-        <x:v>0.14</x:v>
+        <x:v>0.0672</x:v>
       </x:c>
       <x:c r="V9" t="n">
         <x:v>1</x:v>
@@ -1215,7 +1215,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Y9" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="Z9" t="n">
         <x:v>0.25</x:v>
@@ -1224,7 +1224,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="AB9" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.01207</x:v>
       </x:c>
       <x:c r="AC9" t="n">
         <x:v>20</x:v>
@@ -1253,10 +1253,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
       </x:c>
       <x:c r="D10" t="n">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E10" t="n">
         <x:v>10</x:v>
@@ -1283,7 +1283,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M10" t="n">
-        <x:v>0.085</x:v>
+        <x:v>0.053125</x:v>
       </x:c>
       <x:c r="N10" t="n">
         <x:v>0.9</x:v>
@@ -1295,19 +1295,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q10" t="n">
-        <x:v>175</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="R10" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S10" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T10" t="n">
         <x:v>4.5</x:v>
       </x:c>
       <x:c r="U10" t="n">
-        <x:v>0.14</x:v>
+        <x:v>0.0672</x:v>
       </x:c>
       <x:c r="V10" t="n">
         <x:v>1</x:v>
@@ -1319,7 +1319,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Y10" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="Z10" t="n">
         <x:v>0.25</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="AB10" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.01207</x:v>
       </x:c>
       <x:c r="AC10" t="n">
         <x:v>20</x:v>
@@ -1357,10 +1357,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>0|1|2|4|5|7|9|10|12|13</x:v>
+        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
       </x:c>
       <x:c r="D11" t="n">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E11" t="n">
         <x:v>10</x:v>
@@ -1387,7 +1387,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="M11" t="n">
-        <x:v>0.085</x:v>
+        <x:v>0.053125</x:v>
       </x:c>
       <x:c r="N11" t="n">
         <x:v>0.9</x:v>
@@ -1399,19 +1399,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q11" t="n">
-        <x:v>175</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="R11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T11" t="n">
         <x:v>4.5</x:v>
       </x:c>
       <x:c r="U11" t="n">
-        <x:v>0.14</x:v>
+        <x:v>0.0672</x:v>
       </x:c>
       <x:c r="V11" t="n">
         <x:v>1</x:v>
@@ -1423,7 +1423,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Y11" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="Z11" t="n">
         <x:v>0.25</x:v>
@@ -1432,7 +1432,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="AB11" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.01207</x:v>
       </x:c>
       <x:c r="AC11" t="n">
         <x:v>20</x:v>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Ra394f54386cd4331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Rc22cf4b82ce04f48"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -918,7 +918,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD6" s="8" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="AE6" s="8" t="n">
         <x:v>1</x:v>
@@ -1022,7 +1022,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD7" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="AE7" t="n">
         <x:v>1</x:v>
@@ -1126,7 +1126,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD8" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="AE8" t="n">
         <x:v>1</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD9" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="AE9" t="n">
         <x:v>1</x:v>
@@ -1334,7 +1334,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD10" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="AE10" t="n">
         <x:v>1</x:v>
@@ -1438,7 +1438,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AD11" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="AE11" t="n">
         <x:v>1</x:v>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Rc22cf4b82ce04f48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Ra0dcbc6fe5d9494d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -47,7 +47,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -70,6 +70,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -307,6 +316,10 @@
     <x:col min="32" max="32" width="21.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="33" max="33" width="21.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="34" max="34" width="21.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="62.5" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="23.75" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="23.75" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="23.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
@@ -412,6 +425,18 @@
       <x:c r="AH1" s="6" t="str">
         <x:v>波末衔接下一波基础血量</x:v>
       </x:c>
+      <x:c r="AI1" s="9" t="str">
+        <x:v>各次升级所需经验</x:v>
+      </x:c>
+      <x:c r="AJ1" s="9" t="str">
+        <x:v>普通怪击退经验</x:v>
+      </x:c>
+      <x:c r="AK1" s="9" t="str">
+        <x:v>精英击退经验</x:v>
+      </x:c>
+      <x:c r="AL1" s="9" t="str">
+        <x:v>首领击退经验</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="40" customHeight="1">
       <x:c r="A2" s="5" t="str">
@@ -514,6 +539,18 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="AH2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AI2" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AJ2" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AK2" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AL2" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -620,6 +657,18 @@
       <x:c r="AH3" s="6" t="str">
         <x:v>int</x:v>
       </x:c>
+      <x:c r="AI3" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="AJ3" s="9" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="AK3" s="9" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="AL3" s="9" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="5" t="str">
@@ -724,6 +773,18 @@
       <x:c r="AH4" s="6" t="str">
         <x:v>phaseFollowNextWave</x:v>
       </x:c>
+      <x:c r="AI4" s="9" t="str">
+        <x:v>各次升级所需经验</x:v>
+      </x:c>
+      <x:c r="AJ4" s="9" t="str">
+        <x:v>普通怪击退经验</x:v>
+      </x:c>
+      <x:c r="AK4" s="9" t="str">
+        <x:v>精英击退经验</x:v>
+      </x:c>
+      <x:c r="AL4" s="9" t="str">
+        <x:v>首领击退经验</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="40" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -828,6 +889,18 @@
       <x:c r="AH5" s="6" t="str">
         <x:v>phaseFollowNextWave</x:v>
       </x:c>
+      <x:c r="AI5" s="9" t="str">
+        <x:v>supplyXpSteps</x:v>
+      </x:c>
+      <x:c r="AJ5" s="9" t="str">
+        <x:v>normalXp</x:v>
+      </x:c>
+      <x:c r="AK5" s="9" t="str">
+        <x:v>eliteXp</x:v>
+      </x:c>
+      <x:c r="AL5" s="9" t="str">
+        <x:v>bossXp</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="40" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -837,7 +910,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="7" t="n">
         <x:v>18</x:v>
@@ -931,6 +1004,18 @@
       </x:c>
       <x:c r="AH6" s="8" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI6" s="10" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ6" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK6" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL6" s="10" t="n">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -941,7 +1026,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" t="n">
         <x:v>18</x:v>
@@ -1035,6 +1120,18 @@
       </x:c>
       <x:c r="AH7" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI7" s="11" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ7" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK7" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL7" s="11" t="n">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1045,7 +1142,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" t="n">
         <x:v>18</x:v>
@@ -1139,6 +1236,18 @@
       </x:c>
       <x:c r="AH8" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI8" s="11" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ8" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK8" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL8" s="11" t="n">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1149,7 +1258,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D9" t="n">
         <x:v>18</x:v>
@@ -1243,6 +1352,18 @@
       </x:c>
       <x:c r="AH9" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI9" s="11" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ9" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK9" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL9" s="11" t="n">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1253,7 +1374,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D10" t="n">
         <x:v>28</x:v>
@@ -1347,6 +1468,18 @@
       </x:c>
       <x:c r="AH10" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI10" s="11" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ10" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK10" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL10" s="11" t="n">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1357,7 +1490,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>0|2|4|8|10|14|18|20|24|26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D11" t="n">
         <x:v>28</x:v>
@@ -1451,6 +1584,18 @@
       </x:c>
       <x:c r="AH11" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI11" s="11" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ11" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK11" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL11" s="11" t="n">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/ChallengeRule.xlsx
+++ b/design/tables/ChallengeRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="Ra0dcbc6fe5d9494d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeRule" sheetId="1" r:id="R03a88a2a0f4e42ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -907,7 +907,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="7" t="n">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
         <x:v>0</x:v>
@@ -1023,7 +1023,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" t="n">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" t="str">
         <x:v>0</x:v>
@@ -1139,7 +1139,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" t="n">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" t="str">
         <x:v>0</x:v>
@@ -1255,7 +1255,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" t="n">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>0</x:v>
@@ -1371,7 +1371,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C10" t="str">
         <x:v>0</x:v>
@@ -1487,7 +1487,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" t="n">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C11" t="str">
         <x:v>0</x:v>
@@ -1595,6 +1595,470 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL11" s="11" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H12" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="8" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K12" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L12" s="8" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M12" s="8" t="n">
+        <x:v>0.053125</x:v>
+      </x:c>
+      <x:c r="N12" s="8" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O12" s="8" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P12" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q12" s="8" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="R12" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S12" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T12" s="8" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="U12" s="8" t="n">
+        <x:v>0.0672</x:v>
+      </x:c>
+      <x:c r="V12" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W12" s="8" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X12" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y12" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Z12" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA12" s="8" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB12" s="8" t="n">
+        <x:v>0.01207</x:v>
+      </x:c>
+      <x:c r="AC12" s="8" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AD12" s="8" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="AE12" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF12" s="8" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG12" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH12" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI12" s="10" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ12" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK12" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL12" s="10" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C13" s="7" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F13" s="7" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H13" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I13" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="8" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K13" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L13" s="8" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M13" s="8" t="n">
+        <x:v>0.053125</x:v>
+      </x:c>
+      <x:c r="N13" s="8" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O13" s="8" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P13" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q13" s="8" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="R13" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S13" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T13" s="8" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="U13" s="8" t="n">
+        <x:v>0.0672</x:v>
+      </x:c>
+      <x:c r="V13" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W13" s="8" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X13" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y13" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Z13" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA13" s="8" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB13" s="8" t="n">
+        <x:v>0.01207</x:v>
+      </x:c>
+      <x:c r="AC13" s="8" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AD13" s="8" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="AE13" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF13" s="8" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG13" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH13" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI13" s="10" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ13" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK13" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL13" s="10" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H14" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="8" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K14" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L14" s="8" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M14" s="8" t="n">
+        <x:v>0.053125</x:v>
+      </x:c>
+      <x:c r="N14" s="8" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O14" s="8" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P14" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q14" s="8" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="R14" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S14" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T14" s="8" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="U14" s="8" t="n">
+        <x:v>0.0672</x:v>
+      </x:c>
+      <x:c r="V14" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W14" s="8" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X14" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y14" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Z14" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA14" s="8" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB14" s="8" t="n">
+        <x:v>0.01207</x:v>
+      </x:c>
+      <x:c r="AC14" s="8" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AD14" s="8" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="AE14" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF14" s="8" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG14" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH14" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI14" s="10" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ14" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK14" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL14" s="10" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F15" s="7" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I15" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="8" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K15" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L15" s="8" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="M15" s="8" t="n">
+        <x:v>0.053125</x:v>
+      </x:c>
+      <x:c r="N15" s="8" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O15" s="8" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="P15" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q15" s="8" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="R15" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S15" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T15" s="8" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="U15" s="8" t="n">
+        <x:v>0.0672</x:v>
+      </x:c>
+      <x:c r="V15" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W15" s="8" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="X15" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Y15" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Z15" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AA15" s="8" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="AB15" s="8" t="n">
+        <x:v>0.01207</x:v>
+      </x:c>
+      <x:c r="AC15" s="8" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AD15" s="8" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="AE15" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF15" s="8" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="AG15" s="8" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AH15" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI15" s="10" t="str">
+        <x:v>80|105|130|155|180|205|230|255|280|305|330|355|380|405|430|455|480|505|530</x:v>
+      </x:c>
+      <x:c r="AJ15" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK15" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL15" s="10" t="n">
         <x:v>40</x:v>
       </x:c>
     </x:row>
